--- a/TestCase/Instagram.xlsx
+++ b/TestCase/Instagram.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\SDET_Wipro\TestCase\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4F353DD-C048-49AD-9135-CB849F1C0486}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41A61CDF-18A0-440C-AA27-A86A0D93F9EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="147">
   <si>
     <t>Test Case NO</t>
   </si>
@@ -299,6 +299,177 @@
   </si>
   <si>
     <t>Invalid username or password or both or null invaild</t>
+  </si>
+  <si>
+    <t>TC017</t>
+  </si>
+  <si>
+    <t>Verify follow user feature</t>
+  </si>
+  <si>
+    <t>Check user can follow another account</t>
+  </si>
+  <si>
+    <t>1. Search any user 2. Open profile 3. Tap follow button</t>
+  </si>
+  <si>
+    <t>Valid Instagram account</t>
+  </si>
+  <si>
+    <t>User followed successfully</t>
+  </si>
+  <si>
+    <t>TC018</t>
+  </si>
+  <si>
+    <t>Verify save post feature</t>
+  </si>
+  <si>
+    <t>Check user can save any post</t>
+  </si>
+  <si>
+    <t>1. Open any post 2. Tap save icon</t>
+  </si>
+  <si>
+    <t>Post saved successfully</t>
+  </si>
+  <si>
+    <t>TC019</t>
+  </si>
+  <si>
+    <t>Verify share post to story</t>
+  </si>
+  <si>
+    <t>Check user can share post on story</t>
+  </si>
+  <si>
+    <t>1. Open any post 2. Tap share icon 3. Select add to story</t>
+  </si>
+  <si>
+    <t>Post shared to story successfully</t>
+  </si>
+  <si>
+    <t>TC013</t>
+  </si>
+  <si>
+    <t>TC014</t>
+  </si>
+  <si>
+    <t>TC015</t>
+  </si>
+  <si>
+    <t>TC020</t>
+  </si>
+  <si>
+    <t>Verify archive story feature</t>
+  </si>
+  <si>
+    <t>Check user can archive story</t>
+  </si>
+  <si>
+    <t>1. Upload story 2. Open story settings 3. Enable archive</t>
+  </si>
+  <si>
+    <t>Story archived successfully</t>
+  </si>
+  <si>
+    <t>TC021</t>
+  </si>
+  <si>
+    <t>Verify block user feature</t>
+  </si>
+  <si>
+    <t>Check user can block another account</t>
+  </si>
+  <si>
+    <t>1. Open user profile 2. Tap options 3. Tap block</t>
+  </si>
+  <si>
+    <t>User blocked successfully</t>
+  </si>
+  <si>
+    <t>TC022</t>
+  </si>
+  <si>
+    <t>Verify close friends story</t>
+  </si>
+  <si>
+    <t>Check user can share story with close friends</t>
+  </si>
+  <si>
+    <t>1. Add users to close friends 2. Upload story 3. Select close friends</t>
+  </si>
+  <si>
+    <t>Story visible only to close friends</t>
+  </si>
+  <si>
+    <t>TC023</t>
+  </si>
+  <si>
+    <t>Verify unsend message feature</t>
+  </si>
+  <si>
+    <t>Check user can unsend message in chat</t>
+  </si>
+  <si>
+    <t>1. Open chat 2. Long press message 3. Tap unsend</t>
+  </si>
+  <si>
+    <t>Message removed successfully</t>
+  </si>
+  <si>
+    <t>Verify hashtag search</t>
+  </si>
+  <si>
+    <t>Check user can search using hashtag</t>
+  </si>
+  <si>
+    <t>1. Open search 2. Enter hashtag keyword</t>
+  </si>
+  <si>
+    <t>Valid hashtag</t>
+  </si>
+  <si>
+    <t>Related hashtag posts displayed</t>
+  </si>
+  <si>
+    <t>Verify tag user in post</t>
+  </si>
+  <si>
+    <t>Check user can tag another user in post</t>
+  </si>
+  <si>
+    <t>1. Create post 2. Tap tag people 3. Select user 4. Share post</t>
+  </si>
+  <si>
+    <t>User tagged successfully</t>
+  </si>
+  <si>
+    <t>Verify mute account feature</t>
+  </si>
+  <si>
+    <t>Check user can mute another account</t>
+  </si>
+  <si>
+    <t>1. Open profile 2. Tap following 3. Tap mute</t>
+  </si>
+  <si>
+    <t>Account muted successfully</t>
+  </si>
+  <si>
+    <t>Verify pin chat feature</t>
+  </si>
+  <si>
+    <t>Check user can pin chat in inbox</t>
+  </si>
+  <si>
+    <t>1. Open inbox 2. Long press chat 3. Tap pin</t>
+  </si>
+  <si>
+    <t>Chat pinned successfully</t>
+  </si>
+  <si>
+    <t>TC016</t>
   </si>
 </sst>
 </file>
@@ -346,7 +517,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -364,6 +535,9 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -646,14 +820,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H15"/>
+  <dimension ref="A1:H24"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
     <col min="2" max="2" width="21.5703125" style="1" customWidth="1"/>
     <col min="3" max="3" width="24.140625" style="1" customWidth="1"/>
     <col min="4" max="4" width="34" style="1" customWidth="1"/>
-    <col min="5" max="5" width="32.140625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="26.42578125" style="1" customWidth="1"/>
     <col min="6" max="6" width="40.5703125" style="1" customWidth="1"/>
     <col min="7" max="7" width="29.42578125" style="1" customWidth="1"/>
     <col min="8" max="8" width="31.5703125" style="1" customWidth="1"/>
@@ -998,8 +1172,291 @@
         <v>87</v>
       </c>
     </row>
+    <row r="14" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+      <c r="A14" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="D14" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="E14" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="F14" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="G14" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="H14" s="7" t="s">
+        <v>95</v>
+      </c>
+    </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="D15" s="3"/>
+      <c r="A15" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="B15" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="C15" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="D15" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="E15" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="F15" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="G15" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="H15" s="7" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+      <c r="A16" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="B16" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="C16" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="D16" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="E16" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="F16" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="G16" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="H16" s="7" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+      <c r="A17" s="5" t="s">
+        <v>146</v>
+      </c>
+      <c r="B17" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="C17" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="D17" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="E17" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="F17" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="G17" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="H17" s="7" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+      <c r="A18" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="B18" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="C18" s="7" t="s">
+        <v>115</v>
+      </c>
+      <c r="D18" s="7" t="s">
+        <v>116</v>
+      </c>
+      <c r="E18" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="F18" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="G18" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="H18" s="7" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+      <c r="A19" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="B19" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="C19" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="D19" s="7" t="s">
+        <v>121</v>
+      </c>
+      <c r="E19" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="F19" s="7" t="s">
+        <v>122</v>
+      </c>
+      <c r="G19" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="H19" s="7" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+      <c r="A20" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="B20" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="C20" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="D20" s="7" t="s">
+        <v>126</v>
+      </c>
+      <c r="E20" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="F20" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="G20" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="H20" s="7" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="B21" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="C21" s="7" t="s">
+        <v>129</v>
+      </c>
+      <c r="D21" s="7" t="s">
+        <v>130</v>
+      </c>
+      <c r="E21" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="F21" s="7" t="s">
+        <v>131</v>
+      </c>
+      <c r="G21" s="7" t="s">
+        <v>132</v>
+      </c>
+      <c r="H21" s="7" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+      <c r="A22" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="B22" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="C22" s="7" t="s">
+        <v>134</v>
+      </c>
+      <c r="D22" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="E22" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="F22" s="7" t="s">
+        <v>136</v>
+      </c>
+      <c r="G22" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="H22" s="7" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+      <c r="A23" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="B23" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="C23" s="7" t="s">
+        <v>138</v>
+      </c>
+      <c r="D23" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="E23" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="F23" s="7" t="s">
+        <v>140</v>
+      </c>
+      <c r="G23" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="H23" s="7" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="B24" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="C24" s="7" t="s">
+        <v>142</v>
+      </c>
+      <c r="D24" s="7" t="s">
+        <v>143</v>
+      </c>
+      <c r="E24" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="F24" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="G24" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="H24" s="7" t="s">
+        <v>145</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
